--- a/storage/app/arrival.xlsx
+++ b/storage/app/arrival.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\storage\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD7BCF-0DC6-4DAA-B9DD-E1C2274C3C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DB5245-4DCA-43F3-AFA9-9CFD403EF9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{40B8E598-FF4C-42F0-AAB6-ADD8DE7151F6}"/>
   </bookViews>
